--- a/[deprecated]/Residential/Ontario/Residential lighting.xlsx
+++ b/[deprecated]/Residential/Ontario/Residential lighting.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/daniel_posen_utoronto_ca/Documents/Academia/File Sharing/Alliance Mission - TEMOA/Full team - TEMOA/TEMOA model and data/Data sources/Buildings/Residential/Ontario/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/buildings_sector/[deprecated]/Residential/Ontario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{D855E55B-3092-4C5E-BE27-FE3C12869A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E19C983-712E-4559-886D-EB2E64C153C3}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{D855E55B-3092-4C5E-BE27-FE3C12869A2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC596ECE-8E42-4674-990D-7E3119C61B9B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{ECC515EC-E274-46DD-9FC7-1BF4FB9063CD}"/>
+    <workbookView xWindow="-10335" yWindow="4305" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{ECC515EC-E274-46DD-9FC7-1BF4FB9063CD}"/>
   </bookViews>
   <sheets>
     <sheet name="data units" sheetId="1" r:id="rId1"/>
@@ -590,7 +590,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -672,6 +672,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -695,7 +715,7 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -832,6 +852,9 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="9"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Body: normal cell" xfId="6" xr:uid="{EAC00829-540E-46F9-9F6A-AB6790F704C8}"/>
@@ -1340,7 +1363,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="92" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1364,7 +1387,9 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="B3" s="5">
         <v>2020</v>
       </c>
@@ -1382,8 +1407,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4" s="16">
         <v>2022</v>
@@ -1402,9 +1427,6 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
       <c r="B5">
         <v>2025</v>
       </c>
@@ -1627,6 +1649,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="91"/>
       <c r="B17">
         <v>2050</v>
       </c>
@@ -1644,7 +1667,9 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="A18" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="B18" s="1">
         <v>2020</v>
       </c>
@@ -1662,8 +1687,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>9</v>
+      <c r="A19" t="s">
+        <v>8</v>
       </c>
       <c r="B19" s="16">
         <v>2022</v>
@@ -1682,9 +1707,6 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
       <c r="B20">
         <v>2025</v>
       </c>
@@ -1831,7 +1853,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="92" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1855,7 +1877,9 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="B3" s="5">
         <v>2020</v>
       </c>
@@ -1877,8 +1901,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4" s="16">
         <v>2022</v>
@@ -1901,9 +1925,6 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
       <c r="B5">
         <v>2025</v>
       </c>
@@ -2162,6 +2183,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="91"/>
       <c r="B17">
         <v>2050</v>
       </c>
@@ -2183,7 +2205,9 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
+      <c r="A18" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="B18" s="1">
         <v>2020</v>
       </c>
@@ -2205,8 +2229,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>9</v>
+      <c r="A19" t="s">
+        <v>16</v>
       </c>
       <c r="B19" s="16">
         <v>2022</v>
@@ -2229,9 +2253,6 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
       <c r="B20">
         <v>2025</v>
       </c>
@@ -6027,7 +6048,7 @@
       <c r="E2" t="s">
         <v>33</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="90" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6154,6 +6175,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{554B827C-8E45-46C6-BE7E-1FB44C5171E8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
